--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.02840347017249</v>
+        <v>5.36711556390303</v>
       </c>
       <c r="D2" t="n">
-        <v>32.54842349996399</v>
+        <v>5.289118818744148</v>
       </c>
       <c r="E2" t="n">
-        <v>1.086767657842728</v>
+        <v>0.1765997443994433</v>
       </c>
       <c r="F2" t="n">
-        <v>1.031637831145729</v>
+        <v>0.1676411475611812</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.30880279560413</v>
+        <v>5.737680454285671</v>
       </c>
       <c r="D3" t="n">
-        <v>35.0042891751807</v>
+        <v>5.688196990966865</v>
       </c>
       <c r="E3" t="n">
-        <v>1.086767657842728</v>
+        <v>0.1765997443994433</v>
       </c>
       <c r="F3" t="n">
-        <v>1.031637831145729</v>
+        <v>0.1676411475611812</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.97922433409183</v>
+        <v>5.359123954289923</v>
       </c>
       <c r="D4" t="n">
-        <v>33.26081040858148</v>
+        <v>5.404881691394491</v>
       </c>
       <c r="E4" t="n">
-        <v>1.086767657842728</v>
+        <v>0.1765997443994433</v>
       </c>
       <c r="F4" t="n">
-        <v>1.031637831145729</v>
+        <v>0.1676411475611812</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
